--- a/AAAGameData/DataTables/Level/DefendRouteTable.xlsx
+++ b/AAAGameData/DataTables/Level/DefendRouteTable.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>#</t>
   </si>
@@ -32,10 +32,10 @@
     <t>LevelIdentifier</t>
   </si>
   <si>
-    <t>SourceStrongholdId</t>
-  </si>
-  <si>
-    <t>WaypointStrongholdIds</t>
+    <t>SourceTeleportationId</t>
+  </si>
+  <si>
+    <t>WaypointTeleportationIds</t>
   </si>
   <si>
     <t>int</t>
@@ -59,10 +59,91 @@
     <t>所属关卡标识</t>
   </si>
   <si>
-    <t>固定出兵来源据点ID</t>
-  </si>
-  <si>
-    <t>固定途经据点ID，按行军顺序填写，玩家基地隐含为最终目标</t>
+    <t>固定出兵来源传送点ID</t>
+  </si>
+  <si>
+    <t>固定途经传送点ID，按行军顺序填写；最终目标由运行时当前我方GameEnd建筑动态决定</t>
+  </si>
+  <si>
+    <t>Lv_1_Route_East</t>
+  </si>
+  <si>
+    <t>Lv_1</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2,0</t>
+  </si>
+  <si>
+    <t>Lv_1_Route_North</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Lv_1_Route_West</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Lv_2_Route_West</t>
+  </si>
+  <si>
+    <t>Lv_2</t>
+  </si>
+  <si>
+    <t>Lv_2_Route_SouthWest</t>
+  </si>
+  <si>
+    <t>2,1</t>
+  </si>
+  <si>
+    <t>Lv_2_Route_SouthEast</t>
+  </si>
+  <si>
+    <t>Lv_3_Route_North</t>
+  </si>
+  <si>
+    <t>Lv_3</t>
+  </si>
+  <si>
+    <t>1,0</t>
+  </si>
+  <si>
+    <t>Lv_3_Route_East</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Lv_3_Route_SouthEast</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>3,0</t>
+  </si>
+  <si>
+    <t>LvTest_Route_SouthWest</t>
+  </si>
+  <si>
+    <t>LvTest</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>LvTest_Route_SouthEast</t>
+  </si>
+  <si>
+    <t>LvTest_Route_West</t>
   </si>
 </sst>
 </file>
@@ -108,16 +189,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="12.565289497375488" customWidth="1"/>
+    <col min="2" max="2" width="12.5652894973755" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.938801765441895" customWidth="1"/>
-    <col min="5" max="5" width="14.938801765441895" customWidth="1"/>
-    <col min="6" max="6" width="21.557010650634766" customWidth="1"/>
-    <col min="7" max="7" width="64.28022003173828" customWidth="1"/>
+    <col min="4" max="4" width="14.9388017654419" customWidth="1"/>
+    <col min="5" max="5" width="14.9388017654419" customWidth="1"/>
+    <col min="6" max="6" width="21.5570106506348" customWidth="1"/>
+    <col min="7" max="7" width="64.2802200317383" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -197,6 +278,210 @@
         <v>16</v>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" s="0">
+        <v>1</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="0">
+        <v>2</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="0">
+        <v>3</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0">
+        <v>4</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0">
+        <v>5</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="0">
+        <v>6</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="0">
+        <v>7</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="0">
+        <v>8</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0">
+        <v>9</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="0">
+        <v>10</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="0">
+        <v>11</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0">
+        <v>12</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/AAAGameData/DataTables/Level/DefendRouteTable.xlsx
+++ b/AAAGameData/DataTables/Level/DefendRouteTable.xlsx
@@ -65,85 +65,85 @@
     <t>固定途经传送点ID，按行军顺序填写；最终目标由运行时当前我方GameEnd建筑动态决定</t>
   </si>
   <si>
+    <t>LvTest_Route_SouthEast</t>
+  </si>
+  <si>
+    <t>LvTest</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>LvTest_Route_SouthWest</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>LvTest_Route_West</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>Lv_1_Route_East</t>
   </si>
   <si>
     <t>Lv_1</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>2,0</t>
   </si>
   <si>
     <t>Lv_1_Route_North</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Lv_1_Route_West</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Lv_2_Route_West</t>
+    <t>TP0</t>
   </si>
   <si>
     <t>Lv_2</t>
   </si>
   <si>
-    <t>Lv_2_Route_SouthWest</t>
-  </si>
-  <si>
-    <t>2,1</t>
-  </si>
-  <si>
-    <t>Lv_2_Route_SouthEast</t>
+    <t>TP2</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>TP3</t>
+  </si>
+  <si>
+    <t>TP4</t>
+  </si>
+  <si>
+    <t>Lv_3_Route_East</t>
+  </si>
+  <si>
+    <t>Lv_3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1,0</t>
   </si>
   <si>
     <t>Lv_3_Route_North</t>
   </si>
   <si>
-    <t>Lv_3</t>
-  </si>
-  <si>
-    <t>1,0</t>
-  </si>
-  <si>
-    <t>Lv_3_Route_East</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>Lv_3_Route_SouthEast</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>3,0</t>
-  </si>
-  <si>
-    <t>LvTest_Route_SouthWest</t>
-  </si>
-  <si>
-    <t>LvTest</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>LvTest_Route_SouthEast</t>
-  </si>
-  <si>
-    <t>LvTest_Route_West</t>
   </si>
 </sst>
 </file>
@@ -189,7 +189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -326,7 +326,7 @@
         <v>25</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -340,10 +340,10 @@
         <v>27</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -351,16 +351,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -374,10 +374,10 @@
         <v>27</v>
       </c>
       <c r="F10" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="0" t="s">
         <v>22</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -394,7 +394,7 @@
         <v>22</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -402,16 +402,16 @@
         <v>8</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>32</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -419,16 +419,16 @@
         <v>9</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>32</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -436,16 +436,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -453,16 +453,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E15" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="0" t="s">
         <v>40</v>
-      </c>
-      <c r="F15" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="0" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -470,16 +470,33 @@
         <v>12</v>
       </c>
       <c r="D16" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="0">
+        <v>13</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="0" t="s">
         <v>43</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="0" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Level/DefendRouteTable.xlsx
+++ b/AAAGameData/DataTables/Level/DefendRouteTable.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>#</t>
   </si>
@@ -65,34 +65,34 @@
     <t>固定途经传送点ID，按行军顺序填写；最终目标由运行时当前我方GameEnd建筑动态决定</t>
   </si>
   <si>
-    <t>LvTest_Route_SouthEast</t>
+    <t>0_1_2@SouthWest</t>
   </si>
   <si>
     <t>LvTest</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>1_2@SouthEast</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>LvTest_Route_SouthWest</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>LvTest_Route_West</t>
+    <t>3_2@West</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>Lv_1_Route_East</t>
+    <t>1_2_0@East</t>
   </si>
   <si>
     <t>Lv_1</t>
@@ -101,49 +101,43 @@
     <t>2,0</t>
   </si>
   <si>
-    <t>Lv_1_Route_North</t>
-  </si>
-  <si>
-    <t>Lv_1_Route_West</t>
-  </si>
-  <si>
-    <t>TP0</t>
+    <t>2_0@North</t>
+  </si>
+  <si>
+    <t>3_0@West</t>
   </si>
   <si>
     <t>Lv_2</t>
   </si>
   <si>
-    <t>TP2</t>
+    <t>2_4</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>TP3</t>
-  </si>
-  <si>
-    <t>TP4</t>
-  </si>
-  <si>
-    <t>Lv_3_Route_East</t>
+    <t>3_4</t>
+  </si>
+  <si>
+    <t>2_1_0@North</t>
   </si>
   <si>
     <t>Lv_3</t>
   </si>
   <si>
+    <t>1,0</t>
+  </si>
+  <si>
+    <t>4_3_0@SouthEast</t>
+  </si>
+  <si>
+    <t>3,0</t>
+  </si>
+  <si>
+    <t>5_1_0@East</t>
+  </si>
+  <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>1,0</t>
-  </si>
-  <si>
-    <t>Lv_3_Route_North</t>
-  </si>
-  <si>
-    <t>Lv_3_Route_SouthEast</t>
-  </si>
-  <si>
-    <t>3,0</t>
   </si>
 </sst>
 </file>
@@ -326,7 +320,7 @@
         <v>25</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -340,7 +334,7 @@
         <v>27</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>28</v>
@@ -357,10 +351,10 @@
         <v>27</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -377,7 +371,7 @@
         <v>25</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -385,13 +379,13 @@
         <v>7</v>
       </c>
       <c r="D11" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="0" t="s">
-        <v>32</v>
-      </c>
       <c r="F11" s="0" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>3</v>
@@ -402,16 +396,16 @@
         <v>8</v>
       </c>
       <c r="D12" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="0" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="0" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -419,16 +413,16 @@
         <v>9</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>25</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -436,13 +430,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>3</v>
@@ -453,16 +447,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="0" t="s">
         <v>37</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="0" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -470,16 +464,16 @@
         <v>12</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -487,16 +481,16 @@
         <v>13</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
